--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Newborn.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Newborn.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>ID</t>
   </si>
@@ -56,6 +56,9 @@
   </si>
   <si>
     <t>Source</t>
+  </si>
+  <si>
+    <t>Link</t>
   </si>
 </sst>
 </file>
@@ -387,10 +390,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -432,6 +435,9 @@
       </c>
       <c r="N1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Newborn.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Newborn.xlsx
@@ -390,7 +390,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:15">
@@ -440,6 +440,71 @@
         <v>14</v>
       </c>
     </row>
+    <row r="2" spans="1:15">
+      <c r="A2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3">
+        <f>A2+1</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4">
+        <f t="shared" ref="A4:A12" si="0">A3+1</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Newborn.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Newborn.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="18">
   <si>
     <t>ID</t>
   </si>
@@ -59,6 +59,15 @@
   </si>
   <si>
     <t>Link</t>
+  </si>
+  <si>
+    <t>Mississippi Choctaw</t>
+  </si>
+  <si>
+    <t>Mississipi Blood New Born</t>
+  </si>
+  <si>
+    <t>Dawes Rolls Full Document - Choctaw By Blood - Page 168</t>
   </si>
 </sst>
 </file>
@@ -392,6 +401,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O12"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="19.42578125" customWidth="1"/>
+    <col min="11" max="11" width="25.42578125" customWidth="1"/>
+    <col min="12" max="12" width="28.28515625" customWidth="1"/>
+    <col min="14" max="14" width="53.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15">
       <c r="A1" t="s">
@@ -444,65 +459,207 @@
       <c r="A2">
         <v>1</v>
       </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2">
+        <v>168</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="3" spans="1:15">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
       </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>168</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" t="str">
+        <f>N2</f>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4">
         <f t="shared" ref="A4:A12" si="0">A3+1</f>
         <v>3</v>
       </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4">
+        <v>168</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
+      </c>
+      <c r="N4" t="str">
+        <f t="shared" ref="N4:N12" si="1">N3</f>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
+      <c r="B5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5">
+        <v>168</v>
+      </c>
+      <c r="L5" t="s">
+        <v>16</v>
+      </c>
+      <c r="N5" t="str">
+        <f t="shared" si="1"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="6" spans="1:15">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
+      <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6">
+        <v>168</v>
+      </c>
+      <c r="L6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N6" t="str">
+        <f t="shared" si="1"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="7" spans="1:15">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>168</v>
+      </c>
+      <c r="L7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" t="str">
+        <f t="shared" si="1"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="8" spans="1:15">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8">
+        <v>168</v>
+      </c>
+      <c r="L8" t="s">
+        <v>16</v>
+      </c>
+      <c r="N8" t="str">
+        <f t="shared" si="1"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="9" spans="1:15">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
+      <c r="B9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9">
+        <v>168</v>
+      </c>
+      <c r="L9" t="s">
+        <v>16</v>
+      </c>
+      <c r="N9" t="str">
+        <f t="shared" si="1"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="10" spans="1:15">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>168</v>
+      </c>
+      <c r="L10" t="s">
+        <v>16</v>
+      </c>
+      <c r="N10" t="str">
+        <f t="shared" si="1"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="11" spans="1:15">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>168</v>
+      </c>
+      <c r="L11" t="s">
+        <v>16</v>
+      </c>
+      <c r="N11" t="str">
+        <f t="shared" si="1"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
+      </c>
     </row>
     <row r="12" spans="1:15">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12">
+        <v>168</v>
+      </c>
+      <c r="L12" t="s">
+        <v>16</v>
+      </c>
+      <c r="N12" t="str">
+        <f t="shared" si="1"/>
+        <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
   </sheetData>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Newborn.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Newborn.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
   <si>
     <t>ID</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>Dawes Rolls Full Document - Choctaw By Blood - Page 168</t>
+  </si>
+  <si>
+    <t>Image Name</t>
+  </si>
+  <si>
+    <t>Image Binary</t>
   </si>
 </sst>
 </file>
@@ -399,16 +405,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.42578125" customWidth="1"/>
     <col min="11" max="11" width="25.42578125" customWidth="1"/>
     <col min="12" max="12" width="28.28515625" customWidth="1"/>
     <col min="14" max="14" width="53.28515625" customWidth="1"/>
+    <col min="16" max="16" width="15.7109375" customWidth="1"/>
+    <col min="17" max="17" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:17">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -454,8 +462,14 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
+      <c r="P1" t="s">
+        <v>18</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1</v>
       </c>
@@ -472,7 +486,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:17">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -491,7 +505,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:17">
       <c r="A4">
         <f t="shared" ref="A4:A12" si="0">A3+1</f>
         <v>3</v>
@@ -510,7 +524,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:17">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -529,7 +543,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:17">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -548,7 +562,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:17">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -567,7 +581,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:17">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -586,7 +600,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:17">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -605,7 +619,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:17">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -624,7 +638,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:17">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -643,7 +657,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:17">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>

--- a/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Newborn.xlsx
+++ b/DawesRollsViewer/Dawes Rolls One Document/Choctaw/Mississippi Choctaw Newborn.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="21">
   <si>
     <t>ID</t>
   </si>
@@ -70,10 +70,13 @@
     <t>Dawes Rolls Full Document - Choctaw By Blood - Page 168</t>
   </si>
   <si>
-    <t>Image Name</t>
-  </si>
-  <si>
-    <t>Image Binary</t>
+    <t>ImageBinary</t>
+  </si>
+  <si>
+    <t>ImageName</t>
+  </si>
+  <si>
+    <t>TribeRelationship</t>
   </si>
 </sst>
 </file>
@@ -405,7 +408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19.42578125" customWidth="1"/>
@@ -414,9 +417,10 @@
     <col min="14" max="14" width="53.28515625" customWidth="1"/>
     <col min="16" max="16" width="15.7109375" customWidth="1"/>
     <col min="17" max="17" width="15" customWidth="1"/>
+    <col min="18" max="18" width="20.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,13 +467,16 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q1" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="R1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -486,7 +493,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3">
         <f>A2+1</f>
         <v>2</v>
@@ -505,7 +512,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4">
         <f t="shared" ref="A4:A12" si="0">A3+1</f>
         <v>3</v>
@@ -524,7 +531,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -543,7 +550,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -562,7 +569,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -581,7 +588,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -600,7 +607,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -619,7 +626,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -638,7 +645,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:18">
       <c r="A11">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -657,7 +664,7 @@
         <v>Dawes Rolls Full Document - Choctaw By Blood - Page 168</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:18">
       <c r="A12">
         <f t="shared" si="0"/>
         <v>11</v>
